--- a/outputs/Block5_Largest_Adjustments.xlsx
+++ b/outputs/Block5_Largest_Adjustments.xlsx
@@ -106,73 +106,73 @@
     <t>Model Stability</t>
   </si>
   <si>
+    <t>RHouSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RSenSafResH (&gt;10%)</t>
   </si>
   <si>
-    <t>RHouSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
+    <t>DHouTiltResLR (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RHouTiltResLD (&lt;=1%)</t>
   </si>
   <si>
+    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>RHouTiltResH (&lt;=1%)</t>
   </si>
   <si>
-    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RHouSafResLD (&gt;10%)</t>
   </si>
   <si>
     <t>RSenTiltResLD (&lt;=1%)</t>
   </si>
   <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResLR (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+    <t>House Buckets</t>
   </si>
   <si>
     <t>Senate Buckets</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
     <t>ML Predicted</t>
   </si>
   <si>
     <t>Integer</t>
   </si>
   <si>
+    <t>Moderate-low sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate sensitivity</t>
+  </si>
+  <si>
     <t>High sensitivity</t>
   </si>
   <si>
     <t>Low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate-low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate sensitivity</t>
   </si>
 </sst>
 </file>
@@ -633,79 +633,79 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>10.028</v>
+        <v>171.868</v>
       </c>
       <c r="D2">
-        <v>11.468</v>
+        <v>174.552</v>
       </c>
       <c r="E2">
-        <v>13.28203815275881</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F2">
-        <v>11.6</v>
+        <v>172.6</v>
       </c>
       <c r="G2">
-        <v>10.70483610671818</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>13.28203815275881</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L2">
-        <v>3.050242274051084</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M2">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N2">
-        <v>5.6</v>
+        <v>18.7</v>
       </c>
       <c r="O2" t="s">
         <v>47</v>
       </c>
       <c r="P2">
-        <v>15.15860750983988</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q2">
-        <v>1.141286249557361</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R2">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="S2" t="s">
         <v>48</v>
       </c>
       <c r="T2">
-        <v>1.876569357081072</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U2">
-        <v>-0.158607509839884</v>
+        <v>-0.4018190334304563</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>10.70483610671818</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="X2">
-        <v>2.577202046040632</v>
+        <v>2.409431489050235</v>
       </c>
       <c r="Y2">
-        <v>1.717961847241188</v>
+        <v>3.572843600948687</v>
       </c>
       <c r="Z2">
-        <v>0.8449171621432557</v>
+        <v>0.09754261531547112</v>
       </c>
       <c r="AA2">
-        <v>0.5632214404266095</v>
+        <v>0.1446418005797111</v>
       </c>
       <c r="AB2">
-        <v>0.544686120366265</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC2">
-        <v>47.41063290551929</v>
+        <v>89.22335706647648</v>
       </c>
       <c r="AD2" t="s">
         <v>49</v>
@@ -716,82 +716,82 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>172.1</v>
+        <v>173.496</v>
       </c>
       <c r="D3">
-        <v>175.156</v>
+        <v>170.784</v>
       </c>
       <c r="E3">
-        <v>175.5898630732044</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F3">
-        <v>172.6</v>
+        <v>169.2</v>
       </c>
       <c r="G3">
-        <v>173.5749550722659</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>175.5898630732044</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L3">
-        <v>24.70132137894479</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M3">
         <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="O3" t="s">
         <v>47</v>
       </c>
       <c r="P3">
-        <v>173.8081494148196</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q3">
-        <v>0.9898529811049405</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S3" t="s">
         <v>48</v>
       </c>
       <c r="T3">
-        <v>-1.781713658384717</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U3">
-        <v>0.1918505851803616</v>
+        <v>0.01929604709013688</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>173.5749550722659</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="X3">
-        <v>2.014908000938448</v>
+        <v>1.462681674160791</v>
       </c>
       <c r="Y3">
-        <v>1.589863073204356</v>
+        <v>3.350244424001858</v>
       </c>
       <c r="Z3">
-        <v>0.08157085890376452</v>
+        <v>0.3069725753814032</v>
       </c>
       <c r="AA3">
-        <v>0.06436348277948976</v>
+        <v>0.7031148179135396</v>
       </c>
       <c r="AB3">
-        <v>1.320926276948919</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC3">
-        <v>92.72349650896915</v>
+        <v>64.04255765445993</v>
       </c>
       <c r="AD3" t="s">
         <v>50</v>
@@ -805,79 +805,79 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>172.984</v>
+        <v>9.932</v>
       </c>
       <c r="D4">
-        <v>170.488</v>
+        <v>11.352</v>
       </c>
       <c r="E4">
-        <v>172.6467820636017</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F4">
-        <v>169.2</v>
+        <v>11.6</v>
       </c>
       <c r="G4">
-        <v>171.7793246530184</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>172.6467820636017</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L4">
-        <v>4.764861070548267</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M4">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N4">
-        <v>13.2</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="s">
         <v>47</v>
       </c>
       <c r="P4">
-        <v>174.4769462223457</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q4">
-        <v>1.010600627112006</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R4">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="S4" t="s">
         <v>48</v>
       </c>
       <c r="T4">
-        <v>1.830164158743969</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U4">
-        <v>-0.4769462223457026</v>
+        <v>0.2118155723185868</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>171.7793246530184</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="X4">
-        <v>0.8674574105832846</v>
+        <v>2.265316866342099</v>
       </c>
       <c r="Y4">
-        <v>1.353217936398266</v>
+        <v>2.135247528421919</v>
       </c>
       <c r="Z4">
-        <v>0.1820530331818197</v>
+        <v>0.7426678482602922</v>
       </c>
       <c r="AA4">
-        <v>0.2839994527358924</v>
+        <v>0.7000255509494521</v>
       </c>
       <c r="AB4">
-        <v>0.3609743235263839</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC4">
-        <v>80.43391422492162</v>
+        <v>48.29978656895716</v>
       </c>
       <c r="AD4" t="s">
         <v>51</v>
@@ -888,28 +888,28 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D5">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E5">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F5">
         <v>12.4</v>
       </c>
       <c r="G5">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L5">
         <v>2.351026032651849</v>
@@ -924,10 +924,10 @@
         <v>47</v>
       </c>
       <c r="P5">
-        <v>9.674452691001546</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q5">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -936,37 +936,37 @@
         <v>48</v>
       </c>
       <c r="T5">
-        <v>-1.562127356038731</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U5">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="X5">
-        <v>1.570517285964419</v>
+        <v>1.427692789540352</v>
       </c>
       <c r="Y5">
-        <v>1.236580047040277</v>
+        <v>1.45044534583586</v>
       </c>
       <c r="Z5">
-        <v>0.6680135669076143</v>
+        <v>0.6072637094239147</v>
       </c>
       <c r="AA5">
-        <v>0.5259746297430284</v>
+        <v>0.6169414228900835</v>
       </c>
       <c r="AB5">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC5">
-        <v>53.88597538332969</v>
+        <v>54.29973121083951</v>
       </c>
       <c r="AD5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -974,46 +974,46 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6">
-        <v>1.832</v>
+        <v>1.344</v>
       </c>
       <c r="D6">
-        <v>1.772</v>
+        <v>1.788</v>
       </c>
       <c r="E6">
-        <v>2.554644495322226</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>1.803041458005251</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>2.554644495322226</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L6">
-        <v>1.198624596172324</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="s">
         <v>47</v>
       </c>
       <c r="P6">
-        <v>2.528722469358031</v>
+        <v>1.501280428022223</v>
       </c>
       <c r="Q6">
-        <v>0.9898529811049405</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1022,34 +1022,34 @@
         <v>48</v>
       </c>
       <c r="T6">
-        <v>-0.02592202596419435</v>
+        <v>0.02825555268635682</v>
       </c>
       <c r="U6">
-        <v>-0.5287224693580312</v>
+        <v>0.4987195719777766</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.803041458005251</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="X6">
-        <v>0.7516030373169746</v>
+        <v>0.08526833542527745</v>
       </c>
       <c r="Y6">
-        <v>0.5546444953222256</v>
+        <v>0.5269751246641334</v>
       </c>
       <c r="Z6">
-        <v>0.627054575483547</v>
+        <v>0.04882472535627785</v>
       </c>
       <c r="AA6">
-        <v>0.4627341179994319</v>
+        <v>0.3017464291168656</v>
       </c>
       <c r="AB6">
-        <v>0.7491403726077025</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC6">
-        <v>56.57842736664286</v>
+        <v>87.16674245626311</v>
       </c>
       <c r="AD6" t="s">
         <v>49</v>
@@ -1063,82 +1063,82 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>3.692</v>
+        <v>1.92</v>
       </c>
       <c r="D7">
-        <v>3.192</v>
+        <v>1.584</v>
       </c>
       <c r="E7">
-        <v>3.475459163737268</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="G7">
-        <v>3.450678816710424</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>3.475459163737268</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="L7">
-        <v>0.887818750560327</v>
+        <v>1.157976831184469</v>
       </c>
       <c r="M7">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="s">
         <v>47</v>
       </c>
       <c r="P7">
-        <v>3.440193613933819</v>
+        <v>1.299486100486649</v>
       </c>
       <c r="Q7">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>48</v>
       </c>
       <c r="T7">
-        <v>-0.03526554980344976</v>
+        <v>-0.2220880496308713</v>
       </c>
       <c r="U7">
-        <v>-0.4401936139338187</v>
+        <v>-0.2994861004866491</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>3.450678816710424</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="X7">
-        <v>0.0247803470268444</v>
+        <v>0.2404974249815708</v>
       </c>
       <c r="Y7">
-        <v>0.4754591637372685</v>
+        <v>0.5215741501175204</v>
       </c>
       <c r="Z7">
-        <v>0.02791149320872625</v>
+        <v>0.2076875965951506</v>
       </c>
       <c r="AA7">
-        <v>0.5355362943587225</v>
+        <v>0.4504184678583023</v>
       </c>
       <c r="AB7">
-        <v>0.3551275002241308</v>
+        <v>0.8271263079889064</v>
       </c>
       <c r="AC7">
-        <v>81.41748166151876</v>
+        <v>74.62882184844142</v>
       </c>
       <c r="AD7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1146,82 +1146,82 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>3.184</v>
+        <v>1.904</v>
       </c>
       <c r="D8">
-        <v>4.004</v>
+        <v>1.796</v>
       </c>
       <c r="E8">
-        <v>1.550377686812013</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F8">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="G8">
-        <v>3.579766740594905</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>1.550377686812013</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L8">
-        <v>7.059923274159115</v>
+        <v>1.198624596172324</v>
       </c>
       <c r="M8">
         <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="s">
         <v>47</v>
       </c>
       <c r="P8">
-        <v>1.566812662552681</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="s">
         <v>48</v>
       </c>
       <c r="T8">
-        <v>0.01643497574066832</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U8">
-        <v>0.433187337447319</v>
+        <v>0.4427846049148738</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>3.579766740594905</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="X8">
-        <v>2.029389053782892</v>
+        <v>0.7523761957524733</v>
       </c>
       <c r="Y8">
-        <v>0.4496223131879873</v>
+        <v>0.395749179838075</v>
       </c>
       <c r="Z8">
-        <v>0.2874519984106493</v>
+        <v>0.6276996135029299</v>
       </c>
       <c r="AA8">
-        <v>0.06368657218042365</v>
+        <v>0.3301694134275707</v>
       </c>
       <c r="AB8">
-        <v>0.9289372729156731</v>
+        <v>0.7491403726077025</v>
       </c>
       <c r="AC8">
-        <v>81.12864354622022</v>
+        <v>59.24054223283283</v>
       </c>
       <c r="AD8" t="s">
         <v>51</v>
@@ -1235,79 +1235,79 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>1.9</v>
+        <v>13.532</v>
       </c>
       <c r="D9">
-        <v>1.54</v>
+        <v>12.556</v>
       </c>
       <c r="E9">
-        <v>1.430889012604439</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>11.8</v>
       </c>
       <c r="G9">
-        <v>1.730790973320455</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>1.430889012604439</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L9">
-        <v>1.157976831184469</v>
+        <v>3.125306797245826</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="s">
         <v>47</v>
       </c>
       <c r="P9">
-        <v>1.231964530182992</v>
+        <v>13.11473458118962</v>
       </c>
       <c r="Q9">
-        <v>0.8609783982760665</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="S9" t="s">
         <v>48</v>
       </c>
       <c r="T9">
-        <v>-0.1989244824214469</v>
+        <v>-0.2412221969964765</v>
       </c>
       <c r="U9">
-        <v>-0.2319645301829925</v>
+        <v>-0.1147345811896248</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>1.730790973320455</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="X9">
-        <v>0.2999019607160154</v>
+        <v>0.2950157279673533</v>
       </c>
       <c r="Y9">
-        <v>0.4308890126044393</v>
+        <v>0.3559567781861013</v>
       </c>
       <c r="Z9">
-        <v>0.2589878766479743</v>
+        <v>0.09439576563406053</v>
       </c>
       <c r="AA9">
-        <v>0.3721050378561482</v>
+        <v>0.1138949873656525</v>
       </c>
       <c r="AB9">
-        <v>0.8271263079889064</v>
+        <v>0.6511055827595471</v>
       </c>
       <c r="AC9">
-        <v>74.18717584194117</v>
+        <v>90.37337437343564</v>
       </c>
       <c r="AD9" t="s">
         <v>52</v>
@@ -1318,85 +1318,85 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10">
-        <v>3.54</v>
+        <v>3.784</v>
       </c>
       <c r="D10">
-        <v>4.812</v>
+        <v>3.252</v>
       </c>
       <c r="E10">
-        <v>5.586198698614951</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4.153921090288683</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>5.586198698614951</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L10">
-        <v>2.262338789582505</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="s">
         <v>47</v>
       </c>
       <c r="P10">
-        <v>5.645415907992541</v>
+        <v>3.590592119879259</v>
       </c>
       <c r="Q10">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S10" t="s">
         <v>48</v>
       </c>
       <c r="T10">
-        <v>0.05921720937758934</v>
+        <v>-0.06604255040874341</v>
       </c>
       <c r="U10">
-        <v>0.3545840920074594</v>
+        <v>0.409407880120741</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>4.153921090288683</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="X10">
-        <v>1.432277608326268</v>
+        <v>0.1294004093081114</v>
       </c>
       <c r="Y10">
-        <v>0.4138013013850488</v>
+        <v>0.3433653297119976</v>
       </c>
       <c r="Z10">
-        <v>0.633095986737947</v>
+        <v>0.1457509308363258</v>
       </c>
       <c r="AA10">
-        <v>0.1829086356519627</v>
+        <v>0.3867516083607045</v>
       </c>
       <c r="AB10">
-        <v>0.452467757916501</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC10">
-        <v>62.15552874778314</v>
+        <v>79.44532252176565</v>
       </c>
       <c r="AD10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1404,85 +1404,85 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>0.632</v>
+        <v>0.6</v>
       </c>
       <c r="D11">
-        <v>0.416</v>
+        <v>0.696</v>
       </c>
       <c r="E11">
-        <v>0.6558051063869967</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>0.530474583992273</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.6558051063869967</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L11">
-        <v>0.7620693762924241</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M11">
         <v>1.038416113387647</v>
       </c>
       <c r="N11">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="s">
         <v>47</v>
       </c>
       <c r="P11">
-        <v>0.7484613503089816</v>
+        <v>0.2767323416308665</v>
       </c>
       <c r="Q11">
-        <v>1.141286249557361</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="s">
         <v>48</v>
       </c>
       <c r="T11">
-        <v>0.0926562439219849</v>
+        <v>-0.04729480830888999</v>
       </c>
       <c r="U11">
-        <v>0.2515386496910184</v>
+        <v>-0.2767323416308665</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.530474583992273</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="X11">
-        <v>0.1253305223947238</v>
+        <v>0.3210952571747887</v>
       </c>
       <c r="Y11">
-        <v>0.3441948936130033</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="Z11">
-        <v>0.1644607778421363</v>
+        <v>0.2058525907411766</v>
       </c>
       <c r="AA11">
-        <v>0.4516582142265844</v>
+        <v>0.207732212778432</v>
       </c>
       <c r="AB11">
-        <v>0.95258672036553</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC11">
-        <v>76.72213858724069</v>
+        <v>81.34177543201334</v>
       </c>
       <c r="AD11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1490,46 +1490,46 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12">
-        <v>0.632</v>
+        <v>0.18</v>
       </c>
       <c r="D12">
-        <v>0.416</v>
+        <v>0.264</v>
       </c>
       <c r="E12">
-        <v>0.6558051063869967</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.530474583992273</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>0.6558051063869967</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L12">
-        <v>0.7620693762924241</v>
+        <v>0.4925498319332764</v>
       </c>
       <c r="M12">
         <v>1.038416113387647</v>
       </c>
       <c r="N12">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="s">
         <v>47</v>
       </c>
       <c r="P12">
-        <v>0.7484613503089816</v>
+        <v>0.7802977676584159</v>
       </c>
       <c r="Q12">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -1538,34 +1538,34 @@
         <v>48</v>
       </c>
       <c r="T12">
-        <v>0.0926562439219849</v>
+        <v>0.101489785235631</v>
       </c>
       <c r="U12">
-        <v>0.2515386496910184</v>
+        <v>0.2197022323415841</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>0.530474583992273</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="X12">
-        <v>0.1253305223947238</v>
+        <v>0.4593258761975577</v>
       </c>
       <c r="Y12">
-        <v>0.3441948936130033</v>
+        <v>0.3211920175772152</v>
       </c>
       <c r="Z12">
-        <v>0.1644607778421363</v>
+        <v>0.9325470163997145</v>
       </c>
       <c r="AA12">
-        <v>0.4516582142265844</v>
+        <v>0.6521005525806892</v>
       </c>
       <c r="AB12">
-        <v>0.95258672036553</v>
+        <v>1.231374579833191</v>
       </c>
       <c r="AC12">
-        <v>76.72213858724069</v>
+        <v>43.41388982372007</v>
       </c>
       <c r="AD12" t="s">
         <v>51</v>
@@ -1576,46 +1576,46 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>0.612</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D13">
-        <v>0.732</v>
+        <v>0.408</v>
       </c>
       <c r="E13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F13">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G13">
-        <v>0.6684030088931816</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L13">
-        <v>1.559831022862906</v>
+        <v>0.3921195507989373</v>
       </c>
       <c r="M13">
         <v>1.038416113387647</v>
       </c>
       <c r="N13">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
       </c>
       <c r="P13">
-        <v>0.2835868085528425</v>
+        <v>0.3618566504167141</v>
       </c>
       <c r="Q13">
-        <v>0.8609783982760665</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1624,34 +1624,34 @@
         <v>48</v>
       </c>
       <c r="T13">
-        <v>-0.04579057085721838</v>
+        <v>0.04706505036799469</v>
       </c>
       <c r="U13">
-        <v>-0.2835868085528425</v>
+        <v>-0.3618566504167141</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>0.6684030088931816</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="X13">
-        <v>0.3390256294831208</v>
+        <v>0.1737645886865837</v>
       </c>
       <c r="Y13">
-        <v>0.3293773794100608</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="Z13">
-        <v>0.2173476642751179</v>
+        <v>0.4431418640884933</v>
       </c>
       <c r="AA13">
-        <v>0.2111622185879616</v>
+        <v>0.8027949624223952</v>
       </c>
       <c r="AB13">
-        <v>1.299859185719089</v>
+        <v>0.6535325846648956</v>
       </c>
       <c r="AC13">
-        <v>80.63940515159102</v>
+        <v>56.60796713936882</v>
       </c>
       <c r="AD13" t="s">
         <v>51</v>
@@ -1665,82 +1665,82 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>0.164</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D14">
-        <v>0.268</v>
+        <v>6.752</v>
       </c>
       <c r="E14">
-        <v>0.6905082799680116</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F14">
-        <v>0.2</v>
+        <v>6.6</v>
       </c>
       <c r="G14">
-        <v>0.2128826077074241</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>0.6905082799680116</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L14">
-        <v>0.4925498319332764</v>
+        <v>4.673523904256721</v>
       </c>
       <c r="M14">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
       </c>
       <c r="P14">
-        <v>0.7880676051329962</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q14">
-        <v>1.141286249557361</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S14" t="s">
         <v>48</v>
       </c>
       <c r="T14">
-        <v>0.09755932516498467</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U14">
-        <v>0.2119323948670038</v>
+        <v>-0.2240926546957844</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>0.2128826077074241</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="X14">
-        <v>0.4776256722605874</v>
+        <v>3.491136238698697</v>
       </c>
       <c r="Y14">
-        <v>0.3094917200319884</v>
+        <v>0.3017873197440473</v>
       </c>
       <c r="Z14">
-        <v>0.9697002035020272</v>
+        <v>0.747002970396474</v>
       </c>
       <c r="AA14">
-        <v>0.6283460067730039</v>
+        <v>0.06457382607354901</v>
       </c>
       <c r="AB14">
-        <v>1.231374579833191</v>
+        <v>0.5563718933638954</v>
       </c>
       <c r="AC14">
-        <v>42.73182468197061</v>
+        <v>60.16058574846904</v>
       </c>
       <c r="AD14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1748,85 +1748,85 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15">
-        <v>1.412</v>
+        <v>5.384</v>
       </c>
       <c r="D15">
-        <v>1.808</v>
+        <v>4.436</v>
       </c>
       <c r="E15">
-        <v>1.699906626866217</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F15">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G15">
-        <v>1.603126377165344</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>1.699906626866217</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L15">
-        <v>1.746417103282563</v>
+        <v>2.858585552684069</v>
       </c>
       <c r="M15">
         <v>5.24749619700716</v>
       </c>
       <c r="N15">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
       </c>
       <c r="P15">
-        <v>1.717926703142854</v>
+        <v>4.212305297947762</v>
       </c>
       <c r="Q15">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S15" t="s">
         <v>48</v>
       </c>
       <c r="T15">
-        <v>0.01802007627663649</v>
+        <v>-0.07747785760363346</v>
       </c>
       <c r="U15">
-        <v>0.2820732968571464</v>
+        <v>-0.2123052979477622</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>1.603126377165344</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="X15">
-        <v>0.09678024970087273</v>
+        <v>0.6366718809315675</v>
       </c>
       <c r="Y15">
-        <v>0.3000933731337829</v>
+        <v>0.2897831555513957</v>
       </c>
       <c r="Z15">
-        <v>0.05541645779748992</v>
+        <v>0.2227226959619118</v>
       </c>
       <c r="AA15">
-        <v>0.1718337346615124</v>
+        <v>0.1013729168536879</v>
       </c>
       <c r="AB15">
-        <v>0.7593117840358968</v>
+        <v>0.6972159884595291</v>
       </c>
       <c r="AC15">
-        <v>90.83163983910151</v>
+        <v>83.50611917578671</v>
       </c>
       <c r="AD15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1834,85 +1834,85 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16">
-        <v>0.552</v>
+        <v>0.632</v>
       </c>
       <c r="D16">
-        <v>0.392</v>
+        <v>0.44</v>
       </c>
       <c r="E16">
-        <v>0.2703407362038964</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F16">
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.4767959881424244</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>0.2703407362038964</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L16">
-        <v>0.3921195507989373</v>
+        <v>0.7620693762924241</v>
       </c>
       <c r="M16">
         <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
       </c>
       <c r="P16">
-        <v>0.3085361649247209</v>
+        <v>0.8656925512363728</v>
       </c>
       <c r="Q16">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="s">
         <v>48</v>
       </c>
       <c r="T16">
-        <v>0.03819542872082443</v>
+        <v>0.1125966967311974</v>
       </c>
       <c r="U16">
-        <v>-0.3085361649247209</v>
+        <v>0.1343074487636272</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>0.4767959881424244</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="X16">
-        <v>0.206455251938528</v>
+        <v>0.211340668734266</v>
       </c>
       <c r="Y16">
-        <v>0.2703407362038964</v>
+        <v>0.2469041454948246</v>
       </c>
       <c r="Z16">
-        <v>0.526510987574781</v>
+        <v>0.2773247099397544</v>
       </c>
       <c r="AA16">
-        <v>0.6894344738819614</v>
+        <v>0.3239916904889269</v>
       </c>
       <c r="AB16">
-        <v>0.6535325846648956</v>
+        <v>0.95258672036553</v>
       </c>
       <c r="AC16">
-        <v>55.79230620253968</v>
+        <v>74.55313054289088</v>
       </c>
       <c r="AD16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block5_Largest_Adjustments.xlsx
+++ b/outputs/Block5_Largest_Adjustments.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="54">
   <si>
     <t>Variable</t>
   </si>
@@ -106,51 +106,51 @@
     <t>Model Stability</t>
   </si>
   <si>
+    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RHouSafResH (&gt;10%)</t>
   </si>
   <si>
-    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
+    <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
     <t>RSenSafResH (&gt;10%)</t>
   </si>
   <si>
-    <t>DSenSafResH (&gt;10%)</t>
+    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RHouSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouSafResLR (&gt;10%)</t>
   </si>
   <si>
     <t>DHouTiltResLR (&lt;=1%)</t>
   </si>
   <si>
-    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResLD (&lt;=1%)</t>
-  </si>
-  <si>
     <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResLD (&lt;=1%)</t>
-  </si>
-  <si>
     <t>House Buckets</t>
   </si>
   <si>
@@ -166,13 +166,16 @@
     <t>Moderate-low sensitivity</t>
   </si>
   <si>
+    <t>Low sensitivity</t>
+  </si>
+  <si>
+    <t>High sensitivity</t>
+  </si>
+  <si>
     <t>Moderate sensitivity</t>
   </si>
   <si>
-    <t>High sensitivity</t>
-  </si>
-  <si>
-    <t>Low sensitivity</t>
+    <t>Very high sensitivity</t>
   </si>
 </sst>
 </file>
@@ -633,79 +636,79 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>171.868</v>
+        <v>183.632</v>
       </c>
       <c r="D2">
-        <v>174.552</v>
+        <v>178.672</v>
       </c>
       <c r="E2">
-        <v>175.5728436009487</v>
+        <v>184.2285869624531</v>
       </c>
       <c r="F2">
         <v>172.6</v>
       </c>
       <c r="G2">
-        <v>173.1634121118985</v>
+        <v>181.348317089571</v>
       </c>
       <c r="J2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>175.5728436009487</v>
+        <v>181.348317089571</v>
       </c>
       <c r="L2">
-        <v>24.70132137894479</v>
+        <v>14.61847816170942</v>
       </c>
       <c r="M2">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N2">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="O2" t="s">
         <v>47</v>
       </c>
       <c r="P2">
-        <v>172.4018190334305</v>
+        <v>188.1997118794436</v>
       </c>
       <c r="Q2">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="S2" t="s">
         <v>48</v>
       </c>
       <c r="T2">
-        <v>-3.171024567518231</v>
+        <v>6.851394789872614</v>
       </c>
       <c r="U2">
-        <v>-0.4018190334304563</v>
+        <v>-0.1997118794436403</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>173.1634121118985</v>
+        <v>181.348317089571</v>
       </c>
       <c r="X2">
-        <v>2.409431489050235</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>3.572843600948687</v>
+        <v>6.651682910428974</v>
       </c>
       <c r="Z2">
-        <v>0.09754261531547112</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.1446418005797111</v>
+        <v>0.4550188355345981</v>
       </c>
       <c r="AB2">
-        <v>1.320926276948919</v>
+        <v>0.7734644530004987</v>
       </c>
       <c r="AC2">
-        <v>89.22335706647648</v>
+        <v>85.27775146326397</v>
       </c>
       <c r="AD2" t="s">
         <v>49</v>
@@ -719,79 +722,79 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>173.496</v>
+        <v>173.236</v>
       </c>
       <c r="D3">
-        <v>170.784</v>
+        <v>177.628</v>
       </c>
       <c r="E3">
-        <v>173.6497555759981</v>
+        <v>196.1769522593794</v>
       </c>
       <c r="F3">
-        <v>169.2</v>
+        <v>180.6</v>
       </c>
       <c r="G3">
-        <v>172.1870739018374</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>173.6497555759981</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="L3">
-        <v>4.764861070548267</v>
+        <v>28.14072386543135</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N3">
-        <v>13.2</v>
+        <v>26.4</v>
       </c>
       <c r="O3" t="s">
         <v>47</v>
       </c>
       <c r="P3">
-        <v>176.9807039529099</v>
+        <v>169.5721789744432</v>
       </c>
       <c r="Q3">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R3">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="S3" t="s">
         <v>48</v>
       </c>
       <c r="T3">
-        <v>3.330948376911721</v>
+        <v>-5.685985409146298</v>
       </c>
       <c r="U3">
-        <v>0.01929604709013688</v>
+        <v>0.4278210255567672</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>172.1870739018374</v>
+        <v>175.2581643835895</v>
       </c>
       <c r="X3">
-        <v>1.462681674160791</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>3.350244424001858</v>
+        <v>5.258164383589531</v>
       </c>
       <c r="Z3">
-        <v>0.3069725753814032</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.7031148179135396</v>
+        <v>0.1868524920941628</v>
       </c>
       <c r="AB3">
-        <v>0.3609743235263839</v>
+        <v>1.065936510054218</v>
       </c>
       <c r="AC3">
-        <v>64.04255765445993</v>
+        <v>93.6694236066221</v>
       </c>
       <c r="AD3" t="s">
         <v>50</v>
@@ -805,79 +808,79 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>9.932</v>
+        <v>14.476</v>
       </c>
       <c r="D4">
-        <v>11.352</v>
+        <v>13.084</v>
       </c>
       <c r="E4">
-        <v>12.86475247157808</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="F4">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="G4">
-        <v>10.59943560523598</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>12.86475247157808</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="L4">
-        <v>3.050242274051084</v>
+        <v>2.777213034732671</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="s">
         <v>47</v>
       </c>
       <c r="P4">
-        <v>14.78818442768141</v>
+        <v>9.555673875500363</v>
       </c>
       <c r="Q4">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S4" t="s">
         <v>48</v>
       </c>
       <c r="T4">
-        <v>1.923431956103332</v>
+        <v>-2.591880095681738</v>
       </c>
       <c r="U4">
-        <v>0.2118155723185868</v>
+        <v>-0.5556738755003625</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>10.59943560523598</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="X4">
-        <v>2.265316866342099</v>
+        <v>1.692741181415164</v>
       </c>
       <c r="Y4">
-        <v>2.135247528421919</v>
+        <v>3.1475539711821</v>
       </c>
       <c r="Z4">
-        <v>0.7426678482602922</v>
+        <v>0.6095107434126327</v>
       </c>
       <c r="AA4">
-        <v>0.7000255509494521</v>
+        <v>1.133349848145545</v>
       </c>
       <c r="AB4">
-        <v>0.544686120366265</v>
+        <v>0.7714480652035196</v>
       </c>
       <c r="AC4">
-        <v>48.29978656895716</v>
+        <v>45.25511742057672</v>
       </c>
       <c r="AD4" t="s">
         <v>51</v>
@@ -891,79 +894,79 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>13.288</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D5">
-        <v>12.416</v>
+        <v>10.476</v>
       </c>
       <c r="E5">
-        <v>11.45044534583586</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="F5">
-        <v>12.4</v>
+        <v>11.6</v>
       </c>
       <c r="G5">
-        <v>12.87813813537621</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>11.45044534583586</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="L5">
-        <v>2.351026032651849</v>
+        <v>3.004822768461589</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="s">
         <v>47</v>
       </c>
       <c r="P5">
-        <v>9.779145216252848</v>
+        <v>13.63288708314677</v>
       </c>
       <c r="Q5">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S5" t="s">
         <v>48</v>
       </c>
       <c r="T5">
-        <v>-1.671300129583011</v>
+        <v>2.569643732960854</v>
       </c>
       <c r="U5">
-        <v>0.2208547837471517</v>
+        <v>0.3671129168532268</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>12.87813813537621</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="X5">
-        <v>1.427692789540352</v>
+        <v>1.830349175719354</v>
       </c>
       <c r="Y5">
-        <v>1.45044534583586</v>
+        <v>2.936756649814081</v>
       </c>
       <c r="Z5">
-        <v>0.6072637094239147</v>
+        <v>0.6091371494287687</v>
       </c>
       <c r="AA5">
-        <v>0.6169414228900835</v>
+        <v>0.977347709368444</v>
       </c>
       <c r="AB5">
-        <v>0.6530627868477359</v>
+        <v>0.536575494368141</v>
       </c>
       <c r="AC5">
-        <v>54.29973121083951</v>
+        <v>47.8063913390236</v>
       </c>
       <c r="AD5" t="s">
         <v>51</v>
@@ -977,82 +980,82 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>1.344</v>
+        <v>8.536</v>
       </c>
       <c r="D6">
-        <v>1.788</v>
+        <v>6.736</v>
       </c>
       <c r="E6">
-        <v>1.473024875335867</v>
+        <v>5.242518257955137</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="G6">
-        <v>1.558293210761144</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>1.473024875335867</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="L6">
-        <v>1.746417103282563</v>
+        <v>4.568878458795728</v>
       </c>
       <c r="M6">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="s">
         <v>47</v>
       </c>
       <c r="P6">
-        <v>1.501280428022223</v>
+        <v>7.457194256165481</v>
       </c>
       <c r="Q6">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S6" t="s">
         <v>48</v>
       </c>
       <c r="T6">
-        <v>0.02825555268635682</v>
+        <v>-0.250049848920777</v>
       </c>
       <c r="U6">
-        <v>0.4987195719777766</v>
+        <v>-0.4571942561654811</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.558293210761144</v>
+        <v>7.707244105086258</v>
       </c>
       <c r="X6">
-        <v>0.08526833542527745</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.5269751246641334</v>
+        <v>0.7072441050862581</v>
       </c>
       <c r="Z6">
-        <v>0.04882472535627785</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0.3017464291168656</v>
+        <v>0.1547959989447114</v>
       </c>
       <c r="AB6">
-        <v>0.7593117840358968</v>
+        <v>0.6922543119387468</v>
       </c>
       <c r="AC6">
-        <v>87.16674245626311</v>
+        <v>94.72629105871258</v>
       </c>
       <c r="AD6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1060,82 +1063,82 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7">
-        <v>1.92</v>
+        <v>5.116</v>
       </c>
       <c r="D7">
-        <v>1.584</v>
+        <v>4.152</v>
       </c>
       <c r="E7">
-        <v>1.52157415011752</v>
+        <v>3.0173797501092</v>
       </c>
       <c r="F7">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="J7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>1.52157415011752</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="L7">
-        <v>1.157976831184469</v>
+        <v>2.590285563576617</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N7">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="s">
         <v>47</v>
       </c>
       <c r="P7">
-        <v>1.299486100486649</v>
+        <v>4.520574185716101</v>
       </c>
       <c r="Q7">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S7" t="s">
         <v>48</v>
       </c>
       <c r="T7">
-        <v>-0.2220880496308713</v>
+        <v>-0.1515809905634287</v>
       </c>
       <c r="U7">
-        <v>-0.2994861004866491</v>
+        <v>-0.520574185716101</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>1.762071575099091</v>
+        <v>4.67215517627953</v>
       </c>
       <c r="X7">
-        <v>0.2404974249815708</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>0.5215741501175204</v>
+        <v>0.6721551762795297</v>
       </c>
       <c r="Z7">
-        <v>0.2076875965951506</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.4504184678583023</v>
+        <v>0.2594907626136134</v>
       </c>
       <c r="AB7">
-        <v>0.8271263079889064</v>
+        <v>0.7195237676601712</v>
       </c>
       <c r="AC7">
-        <v>74.62882184844142</v>
+        <v>91.31804553655472</v>
       </c>
       <c r="AD7" t="s">
         <v>50</v>
@@ -1149,82 +1152,82 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>1.904</v>
+        <v>9.212</v>
       </c>
       <c r="D8">
-        <v>1.796</v>
+        <v>11.748</v>
       </c>
       <c r="E8">
-        <v>2.604250820161925</v>
+        <v>14.36529697727345</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>13.2</v>
       </c>
       <c r="G8">
-        <v>1.851874624409452</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="J8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>2.604250820161925</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="L8">
-        <v>1.198624596172324</v>
+        <v>5.848565661247161</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N8">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O8" t="s">
         <v>47</v>
       </c>
       <c r="P8">
-        <v>2.557215395085126</v>
+        <v>10.77177037254729</v>
       </c>
       <c r="Q8">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S8" t="s">
         <v>48</v>
       </c>
       <c r="T8">
-        <v>-0.04703542507679881</v>
+        <v>0.3921454006021552</v>
       </c>
       <c r="U8">
-        <v>0.4427846049148738</v>
+        <v>0.2282296274527074</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>1.851874624409452</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="X8">
-        <v>0.7523761957524733</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>0.395749179838075</v>
+        <v>0.6203750280548626</v>
       </c>
       <c r="Z8">
-        <v>0.6276996135029299</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0.3301694134275707</v>
+        <v>0.1060730209742695</v>
       </c>
       <c r="AB8">
-        <v>0.7491403726077025</v>
+        <v>0.7132397147862392</v>
       </c>
       <c r="AC8">
-        <v>59.24054223283283</v>
+        <v>96.35551463316079</v>
       </c>
       <c r="AD8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1232,82 +1235,82 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>13.532</v>
+        <v>2.432</v>
       </c>
       <c r="D9">
-        <v>12.556</v>
+        <v>1.928</v>
       </c>
       <c r="E9">
-        <v>13.3559567781861</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="F9">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>13.06094105021875</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>13.3559567781861</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="L9">
-        <v>3.125306797245826</v>
+        <v>1.357115480819956</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="s">
         <v>47</v>
       </c>
       <c r="P9">
-        <v>13.11473458118962</v>
+        <v>1.265242685482676</v>
       </c>
       <c r="Q9">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R9">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>48</v>
       </c>
       <c r="T9">
-        <v>-0.2412221969964765</v>
+        <v>-0.3431843086563835</v>
       </c>
       <c r="U9">
-        <v>-0.1147345811896248</v>
+        <v>-0.2652426854826757</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>13.06094105021875</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="X9">
-        <v>0.2950157279673533</v>
+        <v>0.5934040093875366</v>
       </c>
       <c r="Y9">
-        <v>0.3559567781861013</v>
+        <v>0.6084269941390592</v>
       </c>
       <c r="Z9">
-        <v>0.09439576563406053</v>
+        <v>0.4372538798459565</v>
       </c>
       <c r="AA9">
-        <v>0.1138949873656525</v>
+        <v>0.4483236708577323</v>
       </c>
       <c r="AB9">
-        <v>0.6511055827595471</v>
+        <v>0.9693682005856831</v>
       </c>
       <c r="AC9">
-        <v>90.37337437343564</v>
+        <v>64.33101602736564</v>
       </c>
       <c r="AD9" t="s">
         <v>52</v>
@@ -1318,85 +1321,85 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
-        <v>3.784</v>
+        <v>0.764</v>
       </c>
       <c r="D10">
-        <v>3.252</v>
+        <v>0.532</v>
       </c>
       <c r="E10">
-        <v>3.656634670288002</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>3.527234260979891</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>3.656634670288002</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="L10">
-        <v>0.887818750560327</v>
+        <v>0.4552884680086201</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="s">
         <v>47</v>
       </c>
       <c r="P10">
-        <v>3.590592119879259</v>
+        <v>0.5301779565157876</v>
       </c>
       <c r="Q10">
-        <v>0.981938980411313</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S10" t="s">
         <v>48</v>
       </c>
       <c r="T10">
-        <v>-0.06604255040874341</v>
+        <v>0.09993249815726635</v>
       </c>
       <c r="U10">
-        <v>0.409407880120741</v>
+        <v>0.4698220434842124</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>3.527234260979891</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="X10">
-        <v>0.1294004093081114</v>
+        <v>0.2278037337410229</v>
       </c>
       <c r="Y10">
-        <v>0.3433653297119976</v>
+        <v>0.5697545416414788</v>
       </c>
       <c r="Z10">
-        <v>0.1457509308363258</v>
+        <v>0.5003503267662599</v>
       </c>
       <c r="AA10">
-        <v>0.3867516083607045</v>
+        <v>1.251414392579545</v>
       </c>
       <c r="AB10">
-        <v>0.3551275002241308</v>
+        <v>0.7588141133477002</v>
       </c>
       <c r="AC10">
-        <v>79.44532252176565</v>
+        <v>46.61616811374733</v>
       </c>
       <c r="AD10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1404,85 +1407,85 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>1.96</v>
       </c>
       <c r="D11">
-        <v>0.696</v>
+        <v>3.288</v>
       </c>
       <c r="E11">
-        <v>0.3240271499397565</v>
+        <v>1.85838186252915</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="G11">
-        <v>0.6451224071145452</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="J11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>0.3240271499397565</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="L11">
-        <v>1.559831022862906</v>
+        <v>3.037968256748472</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N11">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="s">
         <v>47</v>
       </c>
       <c r="P11">
-        <v>0.2767323416308665</v>
+        <v>2.66858738323837</v>
       </c>
       <c r="Q11">
-        <v>0.8540406002469759</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="s">
         <v>48</v>
       </c>
       <c r="T11">
-        <v>-0.04729480830888999</v>
+        <v>0.09714970076867679</v>
       </c>
       <c r="U11">
-        <v>-0.2767323416308665</v>
+        <v>0.33141261676163</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.6451224071145452</v>
+        <v>2.571437682469693</v>
       </c>
       <c r="X11">
-        <v>0.3210952571747887</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.3240271499397565</v>
+        <v>0.4285623175303068</v>
       </c>
       <c r="Z11">
-        <v>0.2058525907411766</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0.207732212778432</v>
+        <v>0.1410687279494473</v>
       </c>
       <c r="AB11">
-        <v>1.299859185719089</v>
+        <v>0.6604278819018417</v>
       </c>
       <c r="AC11">
-        <v>81.34177543201334</v>
+        <v>95.18250283981683</v>
       </c>
       <c r="AD11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1493,31 +1496,31 @@
         <v>46</v>
       </c>
       <c r="C12">
-        <v>0.18</v>
+        <v>0.132</v>
       </c>
       <c r="D12">
-        <v>0.264</v>
+        <v>0.236</v>
       </c>
       <c r="E12">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="F12">
         <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.2194821062252271</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>0.6788079824227848</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="L12">
-        <v>0.4925498319332764</v>
+        <v>0.4196830443219419</v>
       </c>
       <c r="M12">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N12">
         <v>0.4</v>
@@ -1526,10 +1529,10 @@
         <v>47</v>
       </c>
       <c r="P12">
-        <v>0.7802977676584159</v>
+        <v>0.7759837911047821</v>
       </c>
       <c r="Q12">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -1538,37 +1541,37 @@
         <v>48</v>
       </c>
       <c r="T12">
-        <v>0.101489785235631</v>
+        <v>0.1462640945773422</v>
       </c>
       <c r="U12">
-        <v>0.2197022323415841</v>
+        <v>0.2240162088952179</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>0.2194821062252271</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="X12">
-        <v>0.4593258761975577</v>
+        <v>0.4502245067789596</v>
       </c>
       <c r="Y12">
-        <v>0.3211920175772152</v>
+        <v>0.3702803034725601</v>
       </c>
       <c r="Z12">
-        <v>0.9325470163997145</v>
+        <v>1.072772686126412</v>
       </c>
       <c r="AA12">
-        <v>0.6521005525806892</v>
+        <v>0.8822855926209767</v>
       </c>
       <c r="AB12">
-        <v>1.231374579833191</v>
+        <v>1.049207610804855</v>
       </c>
       <c r="AC12">
-        <v>43.41388982372007</v>
+        <v>36.56414014265842</v>
       </c>
       <c r="AD12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -1576,85 +1579,85 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="D13">
-        <v>0.408</v>
+        <v>1.436</v>
       </c>
       <c r="E13">
-        <v>0.3147916000487194</v>
+        <v>1.061924546619121</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>0.4885561887353032</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="J13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>0.3147916000487194</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="L13">
-        <v>0.3921195507989373</v>
+        <v>1.18177630190794</v>
       </c>
       <c r="M13">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N13">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
       </c>
       <c r="P13">
-        <v>0.3618566504167141</v>
+        <v>1.402897891440568</v>
       </c>
       <c r="Q13">
-        <v>1.149511773378675</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>48</v>
       </c>
       <c r="T13">
-        <v>0.04706505036799469</v>
+        <v>0.05107238054804397</v>
       </c>
       <c r="U13">
-        <v>-0.3618566504167141</v>
+        <v>-0.4028978914405681</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>0.4885561887353032</v>
+        <v>1.351825510892524</v>
       </c>
       <c r="X13">
-        <v>0.1737645886865837</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>0.3147916000487194</v>
+        <v>0.3518255108925241</v>
       </c>
       <c r="Z13">
-        <v>0.4431418640884933</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.8027949624223952</v>
+        <v>0.2977090590871665</v>
       </c>
       <c r="AB13">
-        <v>0.6535325846648956</v>
+        <v>1.074342092643582</v>
       </c>
       <c r="AC13">
-        <v>56.60796713936882</v>
+        <v>90.10467186858428</v>
       </c>
       <c r="AD13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1665,79 +1668,79 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>8.763999999999999</v>
+        <v>1.748</v>
       </c>
       <c r="D14">
-        <v>6.752</v>
+        <v>3.744</v>
       </c>
       <c r="E14">
-        <v>4.301787319744047</v>
+        <v>-5.9050260855817</v>
       </c>
       <c r="F14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G14">
-        <v>7.792923558442745</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="J14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>4.301787319744047</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="L14">
-        <v>4.673523904256721</v>
+        <v>9.299703921130613</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N14">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
       </c>
       <c r="P14">
-        <v>4.224092654695784</v>
+        <v>2.767758209900166</v>
       </c>
       <c r="Q14">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="s">
         <v>48</v>
       </c>
       <c r="T14">
-        <v>-0.07769466504826283</v>
+        <v>0.1007600064291512</v>
       </c>
       <c r="U14">
-        <v>-0.2240926546957844</v>
+        <v>0.2322417900998337</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>7.792923558442745</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="X14">
-        <v>3.491136238698697</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>0.3017873197440473</v>
+        <v>0.3330017965289849</v>
       </c>
       <c r="Z14">
-        <v>0.747002970396474</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>0.06457382607354901</v>
+        <v>0.03580778478036752</v>
       </c>
       <c r="AB14">
-        <v>0.5563718933638954</v>
+        <v>0.9207627644683776</v>
       </c>
       <c r="AC14">
-        <v>60.16058574846904</v>
+        <v>98.75454828619661</v>
       </c>
       <c r="AD14" t="s">
         <v>50</v>
@@ -1751,82 +1754,82 @@
         <v>45</v>
       </c>
       <c r="C15">
-        <v>5.384</v>
+        <v>1.064</v>
       </c>
       <c r="D15">
-        <v>4.436</v>
+        <v>1.632</v>
       </c>
       <c r="E15">
-        <v>4.289783155551396</v>
+        <v>0.2672118870713838</v>
       </c>
       <c r="F15">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="G15">
-        <v>4.926455036482963</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="J15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>4.289783155551396</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="L15">
-        <v>2.858585552684069</v>
+        <v>1.998268059200945</v>
       </c>
       <c r="M15">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N15">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
       </c>
       <c r="P15">
-        <v>4.212305297947762</v>
+        <v>1.375597021497778</v>
       </c>
       <c r="Q15">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S15" t="s">
         <v>48</v>
       </c>
       <c r="T15">
-        <v>-0.07747785760363346</v>
+        <v>0.05007849465833103</v>
       </c>
       <c r="U15">
-        <v>-0.2123052979477622</v>
+        <v>-0.3755970214977782</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>4.926455036482963</v>
+        <v>1.325518526839447</v>
       </c>
       <c r="X15">
-        <v>0.6366718809315675</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>0.2897831555513957</v>
+        <v>0.3255185268394472</v>
       </c>
       <c r="Z15">
-        <v>0.2227226959619118</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0.1013729168536879</v>
+        <v>0.1629003302838227</v>
       </c>
       <c r="AB15">
-        <v>0.6972159884595291</v>
+        <v>0.8688121996525846</v>
       </c>
       <c r="AC15">
-        <v>83.50611917578671</v>
+        <v>94.45797913689444</v>
       </c>
       <c r="AD15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1834,82 +1837,82 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>0.632</v>
+        <v>12.34</v>
       </c>
       <c r="D16">
-        <v>0.44</v>
+        <v>10.124</v>
       </c>
       <c r="E16">
-        <v>0.7530958545051754</v>
+        <v>9.224776144749352</v>
       </c>
       <c r="F16">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G16">
-        <v>0.5417551857709093</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="J16" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>0.7530958545051754</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="L16">
-        <v>0.7620693762924241</v>
+        <v>5.707606654863389</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N16">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
       </c>
       <c r="P16">
-        <v>0.8656925512363728</v>
+        <v>10.95245860103622</v>
       </c>
       <c r="Q16">
-        <v>1.149511773378675</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S16" t="s">
         <v>48</v>
       </c>
       <c r="T16">
-        <v>0.1125966967311974</v>
+        <v>-0.3672508083366459</v>
       </c>
       <c r="U16">
-        <v>0.1343074487636272</v>
+        <v>0.04754139896378362</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>0.5417551857709093</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="X16">
-        <v>0.211340668734266</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>0.2469041454948246</v>
+        <v>0.3197094093728623</v>
       </c>
       <c r="Z16">
-        <v>0.2773247099397544</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0.3239916904889269</v>
+        <v>0.05601461850922075</v>
       </c>
       <c r="AB16">
-        <v>0.95258672036553</v>
+        <v>0.6876634523931793</v>
       </c>
       <c r="AC16">
-        <v>74.55313054289088</v>
+        <v>98.05858140436257</v>
       </c>
       <c r="AD16" t="s">
         <v>50</v>

--- a/outputs/Block5_Largest_Adjustments.xlsx
+++ b/outputs/Block5_Largest_Adjustments.xlsx
@@ -559,25 +559,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5142079999999999</v>
+        <v>0.5143840000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4958199999999996</v>
+        <v>0.4959679999999996</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4976068069845513</v>
+        <v>0.4972024416993439</v>
       </c>
       <c r="F2" t="n">
         <v>0.4868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5062773903434608</v>
+        <v>0.506441314148639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="I2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="L2" t="n">
         <v>0.01323492690170848</v>
@@ -604,7 +604,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,25 +632,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4576439999999986</v>
+        <v>0.4577239999999985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4753639999999988</v>
+        <v>0.4752239999999988</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4714935259345234</v>
+        <v>0.471947408691133</v>
       </c>
       <c r="F3" t="n">
         <v>0.484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4652865061515034</v>
+        <v>0.4652716217636178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="I3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="L3" t="n">
         <v>0.01064148394560983</v>
@@ -677,7 +677,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1601,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1637,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
